--- a/service_ia/dataset/analyze_none_id.xlsx
+++ b/service_ia/dataset/analyze_none_id.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2557,7 +2557,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1a8a4d5cba8f3bce24d6d95a54ae0b22</t>
+          <t>cc10f9644d1c9502601630c631d645e5</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Feralpisalò</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Brescia</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
@@ -2579,20 +2579,20 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>cc10f9644d1c9502601630c631d645e5</t>
+          <t>e6bed0e734dfbd4b71bea7319ddd398b</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>45185.5</v>
+        <v>45195.77083333334</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Feralpisalò</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -2601,20 +2601,20 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0f6677c041499be59d2ec53483faa374</t>
+          <t>38f787993f73eb2e981f5395e6eed149</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
-        <v>45192.5</v>
+        <v>45228.83333333334</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
@@ -2623,20 +2623,20 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>e6bed0e734dfbd4b71bea7319ddd398b</t>
+          <t>c7b75416400882d1e732fbaf0b826067</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
-        <v>45195.77083333334</v>
+        <v>45262.54166666666</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
@@ -2645,20 +2645,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9315c68ad0093d4396712a16c4d71c7c</t>
+          <t>9851b2a5312eeff2bcf744c27fbe09a7</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
-        <v>45200.59375</v>
+        <v>45262.54166666666</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
+          <t>Feralpisalò</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>Cittadella</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Lecce</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -2667,20 +2667,20 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8c5cd7a538b287f59e9497f9408fb556</t>
+          <t>40b8c9c9879a661ba668957159df2e55</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>45206.5</v>
+        <v>45270.63541666666</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -2689,47 +2689,51 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1ae8fbaccb63a99856a4c71790c20930</t>
+          <t>2d2bfa2b9104720e2a64dcbb1c2bedee</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>45220.5</v>
+        <v>45313.83333333334</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ascoli</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>(759d56247ba153ecf0effd8a5316ba0d,2024-01-20T15:15:00Z)</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>e64700fe6e16ea3447ecf404116e6c3c</t>
+          <t>9caa3304a219d748ed618505349efd92</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>45223.6875</v>
+        <v>45318.60416666666</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>VfL Wolfsburg</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>FC Koln</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>(0c90115bf8b82532ff9026cbcdfa60d6,2023-08-19T12:00:00Z)</t>
+          <t>(1f22f7965a4f105fcc2c21ac49ab4840,2023-08-19T20:00:00Z)</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -2737,20 +2741,20 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>38f787993f73eb2e981f5395e6eed149</t>
+          <t>cbd173f376f1090a5c0f3758f357069e</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>45228.83333333334</v>
+        <v>45318.63541666666</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -2759,20 +2763,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>c7b75416400882d1e732fbaf0b826067</t>
+          <t>afc2c671a93ddba9566e79c61af10390</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
-        <v>45262.54166666666</v>
+        <v>45318.63541666666</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Feralpisalò</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
@@ -2781,20 +2785,20 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9851b2a5312eeff2bcf744c27fbe09a7</t>
+          <t>ca6a5490dcaa15c3eb502b6dc975ba8d</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>45262.54166666666</v>
+        <v>45318.63541666666</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Feralpisalò</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Spezia</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -2803,20 +2807,20 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>40b8c9c9879a661ba668957159df2e55</t>
+          <t>7a771bc16b03a3a4538b66044406d28c</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>45270.63541666666</v>
+        <v>45321.83333333334</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="E104" t="inlineStr"/>
@@ -2825,72 +2829,64 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2d2bfa2b9104720e2a64dcbb1c2bedee</t>
+          <t>efa66ae37c02f3bf92f4da9320a41004</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>45313.83333333334</v>
+        <v>45325.54166666666</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>(759d56247ba153ecf0effd8a5316ba0d,2024-01-20T15:15:00Z)</t>
-        </is>
-      </c>
+          <t>Pisa</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>9caa3304a219d748ed618505349efd92</t>
+          <t>376b02acd619d9eb1e4c83c84ae2d7a4</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>45318.60416666666</v>
+        <v>45325.54166666666</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VfL Wolfsburg</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>FC Koln</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>(1f22f7965a4f105fcc2c21ac49ab4840,2023-08-19T20:00:00Z)</t>
-        </is>
-      </c>
+          <t>Feralpisalò</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>cbd173f376f1090a5c0f3758f357069e</t>
+          <t>cead3cd35dcd1f8d144f47284cb2d27b</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>45318.63541666666</v>
+        <v>45339.54166666666</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -2899,20 +2895,20 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>afc2c671a93ddba9566e79c61af10390</t>
+          <t>559a559e381863ba73d694ae08c37138</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
-        <v>45318.63541666666</v>
+        <v>45339.54166666666</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
           <t>Feralpisalò</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Lecco</t>
         </is>
       </c>
       <c r="E108" t="inlineStr"/>
@@ -2921,20 +2917,20 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ca6a5490dcaa15c3eb502b6dc975ba8d</t>
+          <t>1493cd8f1f18e877cb7f64e159030dac</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>45318.63541666666</v>
+        <v>45346.54166666666</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Feralpisalò</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Spezia</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -2943,20 +2939,20 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>7a771bc16b03a3a4538b66044406d28c</t>
+          <t>d829e5152add4faf5eea9e683291ba74</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>45321.83333333334</v>
+        <v>45346.63541666666</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="E110" t="inlineStr"/>
@@ -2965,20 +2961,20 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>efa66ae37c02f3bf92f4da9320a41004</t>
+          <t>ef5f00c888356f7234518ccd836482e2</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
-        <v>45325.54166666666</v>
+        <v>45354.63541666666</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -2987,20 +2983,20 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>376b02acd619d9eb1e4c83c84ae2d7a4</t>
+          <t>4a2b8ca80665599187d5d99a6df5b8b3</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
-        <v>45325.54166666666</v>
+        <v>45396.66666666666</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Feralpisalò</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3009,20 +3005,20 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>cead3cd35dcd1f8d144f47284cb2d27b</t>
+          <t>20b8fcdde4f882d8861642859658875c</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>45339.54166666666</v>
+        <v>45409.58333333334</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
@@ -3031,20 +3027,20 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>559a559e381863ba73d694ae08c37138</t>
+          <t>2cbfefe662f86d5a4855319f82ca5d3d</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>45339.54166666666</v>
+        <v>45409.58333333334</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Feralpisalò</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -3053,20 +3049,20 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1493cd8f1f18e877cb7f64e159030dac</t>
+          <t>a845275fc5bff5ff103526d3cda166f0</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>45346.54166666666</v>
+        <v>45409.58333333334</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Feralpisalò</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3075,20 +3071,20 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>d829e5152add4faf5eea9e683291ba74</t>
+          <t>17447fa0c145fae9a347a78c794f8184</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>45346.63541666666</v>
+        <v>45409.58333333334</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E116" t="inlineStr"/>
@@ -3097,20 +3093,20 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ef5f00c888356f7234518ccd836482e2</t>
+          <t>afc9ed10dc9c75f2c8b64bdc95a42d41</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
-        <v>45354.63541666666</v>
+        <v>45409.58333333334</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atalanta BC</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
@@ -3119,20 +3115,20 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>4a2b8ca80665599187d5d99a6df5b8b3</t>
+          <t>e58fe7ce4b92a3a3e0d11b926d525c7c</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
-        <v>45396.66666666666</v>
+        <v>45427.83333333334</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3141,20 +3137,20 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>20b8fcdde4f882d8861642859658875c</t>
+          <t>3b61c1bd7f9e4a3c881559163af9c690</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
-        <v>45409.58333333334</v>
+        <v>45430.58333333334</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="E119" t="inlineStr"/>
@@ -3163,15 +3159,15 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2cbfefe662f86d5a4855319f82ca5d3d</t>
+          <t>154ff75441d1e0a6bf01dd0bdf6d323a</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
-        <v>45409.58333333334</v>
+        <v>45430.58333333334</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3185,11 +3181,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>a845275fc5bff5ff103526d3cda166f0</t>
+          <t>f4eb95dbbaf83443dd5165d4cf3b3f49</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
-        <v>45409.58333333334</v>
+        <v>45430.58333333334</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -3198,7 +3194,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
@@ -3207,20 +3203,20 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>17447fa0c145fae9a347a78c794f8184</t>
+          <t>c8681b8636db9fd7c1f797ec95539781</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
-        <v>45409.58333333334</v>
+        <v>45430.58333333334</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Hellas Verona FC</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
@@ -3229,20 +3225,20 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>afc9ed10dc9c75f2c8b64bdc95a42d41</t>
+          <t>7030235bd1383919bdb8af5dccb4e7a3</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>45409.58333333334</v>
+        <v>45430.58333333334</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Atalanta BC</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
@@ -3251,20 +3247,20 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>e58fe7ce4b92a3a3e0d11b926d525c7c</t>
+          <t>bef8b2fec7c1aa08e92018df9725b887</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>45427.83333333334</v>
+        <v>45430.58333333334</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -3273,64 +3269,72 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3b61c1bd7f9e4a3c881559163af9c690</t>
+          <t>fdf881a025736fb2c5e0229166bcf924</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>45430.58333333334</v>
+        <v>45435.77083333334</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>Bari</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>(7cb8024348c9b588c0b347c352f420ac,2023-09-03T16:30:00Z)</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>154ff75441d1e0a6bf01dd0bdf6d323a</t>
+          <t>0d744b13171ca003e98f36c940062fa0</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>45430.58333333334</v>
+        <v>45436.77083333334</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>(df0d4db2b42f8d73f0e8e0d8f2be5507,2023-09-26T18:30:00Z)</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>f4eb95dbbaf83443dd5165d4cf3b3f49</t>
+          <t>3e9f759bd6d55b4a4e34ec1991fec7b7</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
-        <v>45430.58333333334</v>
+        <v>45437.59375</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E127" t="inlineStr"/>
@@ -3339,42 +3343,46 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>c8681b8636db9fd7c1f797ec95539781</t>
+          <t>56165a7053490ec25d32be97ca42403d</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
-        <v>45430.58333333334</v>
+        <v>45445.77083333334</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Hellas Verona FC</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>(382a06dea0ef7f63c8352fc4cdb7ae94,2024-04-26T18:30:00Z)</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>7030235bd1383919bdb8af5dccb4e7a3</t>
+          <t>4393709a37a9a72310ed563cd42d998a</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
-        <v>45430.58333333334</v>
+        <v>45532.8125</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
@@ -3383,94 +3391,90 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>bef8b2fec7c1aa08e92018df9725b887</t>
+          <t>af7a17725792c4574491aba7d52509ce</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
-        <v>45430.58333333334</v>
+        <v>45558.78125</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atalanta BC</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>(274d70ef2ec8be62312783f0e7e413c4,2024-09-22T16:00:00Z)</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>fdf881a025736fb2c5e0229166bcf924</t>
+          <t>b2323f8212a00207122164c1009f8b30</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
-        <v>45435.77083333334</v>
+        <v>45561.79166666666</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Bari</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>(7cb8024348c9b588c0b347c352f420ac,2023-09-03T16:30:00Z)</t>
-        </is>
-      </c>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>0d744b13171ca003e98f36c940062fa0</t>
+          <t>58aec803a664cb7adda06a481ad25762</t>
         </is>
       </c>
       <c r="B132" s="2" t="n">
-        <v>45436.77083333334</v>
+        <v>45571.79166666666</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>(df0d4db2b42f8d73f0e8e0d8f2be5507,2023-09-26T18:30:00Z)</t>
-        </is>
-      </c>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3e9f759bd6d55b4a4e34ec1991fec7b7</t>
+          <t>a978db38e5ce9c6ab3250880f4ccd9cd</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>45437.59375</v>
+        <v>45599.54166666666</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
@@ -3479,46 +3483,42 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>56165a7053490ec25d32be97ca42403d</t>
+          <t>23a163855e2f84e2f07eb7c3e8683398</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
-        <v>45445.77083333334</v>
+        <v>45606.63541666666</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cremonese</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>(382a06dea0ef7f63c8352fc4cdb7ae94,2024-04-26T18:30:00Z)</t>
-        </is>
-      </c>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>4393709a37a9a72310ed563cd42d998a</t>
+          <t>1c60b9f84b232e9ba8f1e0ce324beb4d</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>45532.8125</v>
+        <v>45627.70833333334</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -3527,46 +3527,42 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>af7a17725792c4574491aba7d52509ce</t>
+          <t>d3f58f39ef06747c8b6c0f02b6b18ac2</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>45558.78125</v>
+        <v>45627.70833333334</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Atalanta BC</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>(274d70ef2ec8be62312783f0e7e413c4,2024-09-22T16:00:00Z)</t>
-        </is>
-      </c>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>b2323f8212a00207122164c1009f8b30</t>
+          <t>2d307b051be2650fa8c512451a2e2a71</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
-        <v>45561.79166666666</v>
+        <v>45627.70833333334</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
           <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
@@ -3575,20 +3571,20 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>58aec803a664cb7adda06a481ad25762</t>
+          <t>7f57da1f9494b2bd2dd946e8bec84292</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
-        <v>45571.79166666666</v>
+        <v>45634.83333333334</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
@@ -3597,20 +3593,20 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>a978db38e5ce9c6ab3250880f4ccd9cd</t>
+          <t>9c76b81eaffbd0c20ab7b06a65e09b5e</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
-        <v>45599.54166666666</v>
+        <v>45647.83333333334</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
           <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
         </is>
       </c>
       <c r="E139" t="inlineStr"/>
@@ -3619,20 +3615,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>23a163855e2f84e2f07eb7c3e8683398</t>
+          <t>2d689bb79fcecdbc5d1ff9193738e752</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
-        <v>45606.63541666666</v>
+        <v>45675.72916666666</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Mallorca</t>
+          <t>Celta Vigo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Athletic Bilbao</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
@@ -3641,20 +3637,20 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1c60b9f84b232e9ba8f1e0ce324beb4d</t>
+          <t>efe070a51dde6860045efae2c9f9ce0c</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
-        <v>45627.70833333334</v>
+        <v>45676.54166666666</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Alavés</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
@@ -3663,20 +3659,20 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>d3f58f39ef06747c8b6c0f02b6b18ac2</t>
+          <t>72497c45b8cee1956dfd1158dec11337</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
-        <v>45627.70833333334</v>
+        <v>45697.54166666666</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
@@ -3685,20 +3681,20 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2d307b051be2650fa8c512451a2e2a71</t>
+          <t>e9b5eb29dd50d951908dc345534f7015</t>
         </is>
       </c>
       <c r="B143" s="2" t="n">
-        <v>45627.70833333334</v>
+        <v>45717.72916666666</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="E143" t="inlineStr"/>
@@ -3707,20 +3703,20 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>7f57da1f9494b2bd2dd946e8bec84292</t>
+          <t>82ea1cfa27c95b92641a9d29a883e2ab</t>
         </is>
       </c>
       <c r="B144" s="2" t="n">
-        <v>45634.83333333334</v>
+        <v>45718.58333333334</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E144" t="inlineStr"/>
@@ -3729,20 +3725,20 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>9c76b81eaffbd0c20ab7b06a65e09b5e</t>
+          <t>d001a36f682351a1b9d8fc80b571028c</t>
         </is>
       </c>
       <c r="B145" s="2" t="n">
-        <v>45647.83333333334</v>
+        <v>45718.63541666666</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
@@ -3751,20 +3747,20 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2d689bb79fcecdbc5d1ff9193738e752</t>
+          <t>9505d0a9c9d1afe06b181fe5ca17f24f</t>
         </is>
       </c>
       <c r="B146" s="2" t="n">
-        <v>45675.72916666666</v>
+        <v>45731.67708333334</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Celta Vigo</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Athletic Bilbao</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
@@ -3773,20 +3769,20 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>efe070a51dde6860045efae2c9f9ce0c</t>
+          <t>24fd7fa8e3335a65351d3e8dae6c0732</t>
         </is>
       </c>
       <c r="B147" s="2" t="n">
-        <v>45676.54166666666</v>
+        <v>45753.59375</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Alavés</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
@@ -3795,20 +3791,20 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>72497c45b8cee1956dfd1158dec11337</t>
+          <t>729857e43832ff3b934c7426ee807223</t>
         </is>
       </c>
       <c r="B148" s="2" t="n">
-        <v>45697.54166666666</v>
+        <v>45768.4375</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="E148" t="inlineStr"/>
@@ -3817,20 +3813,20 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>e9b5eb29dd50d951908dc345534f7015</t>
+          <t>6f6293bbf492db6169cfa81ef98cab99</t>
         </is>
       </c>
       <c r="B149" s="2" t="n">
-        <v>45717.72916666666</v>
+        <v>45768.54166666666</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="E149" t="inlineStr"/>
@@ -3839,20 +3835,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>82ea1cfa27c95b92641a9d29a883e2ab</t>
+          <t>b03cae4da7433b7fe256646f695201a4</t>
         </is>
       </c>
       <c r="B150" s="2" t="n">
-        <v>45718.58333333334</v>
+        <v>45768.66666666666</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E150" t="inlineStr"/>
@@ -3861,20 +3857,20 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>d001a36f682351a1b9d8fc80b571028c</t>
+          <t>e2a68f828ff25a069f9432295bf26f21</t>
         </is>
       </c>
       <c r="B151" s="2" t="n">
-        <v>45718.63541666666</v>
+        <v>45768.78125</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="E151" t="inlineStr"/>
@@ -3883,20 +3879,20 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>9505d0a9c9d1afe06b181fe5ca17f24f</t>
+          <t>83b621406141110857e9690920a7fe6d</t>
         </is>
       </c>
       <c r="B152" s="2" t="n">
-        <v>45731.67708333334</v>
+        <v>45772.78125</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Atalanta BC</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -3905,20 +3901,20 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>24fd7fa8e3335a65351d3e8dae6c0732</t>
+          <t>ddeb75146108e1b755ed0030b78a5612</t>
         </is>
       </c>
       <c r="B153" s="2" t="n">
-        <v>45753.59375</v>
+        <v>45773.54166666666</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="E153" t="inlineStr"/>
@@ -3927,20 +3923,20 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>729857e43832ff3b934c7426ee807223</t>
+          <t>ce4e920e1aaa5a0c5329fc2996bfa678</t>
         </is>
       </c>
       <c r="B154" s="2" t="n">
-        <v>45768.4375</v>
+        <v>45773.54166666666</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -3949,20 +3945,20 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>6f6293bbf492db6169cfa81ef98cab99</t>
+          <t>ea580d732237a7eeaeed18161b4a5971</t>
         </is>
       </c>
       <c r="B155" s="2" t="n">
-        <v>45768.54166666666</v>
+        <v>45773.63541666666</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>US Catanzaro 1929</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
@@ -3971,20 +3967,20 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>b03cae4da7433b7fe256646f695201a4</t>
+          <t>3d61cdda97e58eee8fb2f52c363e8a74</t>
         </is>
       </c>
       <c r="B156" s="2" t="n">
-        <v>45768.66666666666</v>
+        <v>45773.66666666666</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="E156" t="inlineStr"/>
@@ -3993,20 +3989,20 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>e2a68f828ff25a069f9432295bf26f21</t>
+          <t>1d11ec7d023cb74d7c9db7be2d2bdf4c</t>
         </is>
       </c>
       <c r="B157" s="2" t="n">
-        <v>45768.78125</v>
+        <v>45773.78125</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
           <t>Parma</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Juventus</t>
         </is>
       </c>
       <c r="E157" t="inlineStr"/>
@@ -4015,20 +4011,20 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>83b621406141110857e9690920a7fe6d</t>
+          <t>13e6d3c39741630996872d9edf36392a</t>
         </is>
       </c>
       <c r="B158" s="2" t="n">
-        <v>45772.78125</v>
+        <v>45792.70833333334</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Atalanta BC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="E158" t="inlineStr"/>
@@ -4037,20 +4033,20 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ddeb75146108e1b755ed0030b78a5612</t>
+          <t>9ad64f2ea5f9848306b5e2e22a903597</t>
         </is>
       </c>
       <c r="B159" s="2" t="n">
-        <v>45773.54166666666</v>
+        <v>45795.54166666666</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Atalanta BC</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4059,208 +4055,76 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ce4e920e1aaa5a0c5329fc2996bfa678</t>
+          <t>0ff442300bab3d44bf09d1e6855a2cae</t>
         </is>
       </c>
       <c r="B160" s="2" t="n">
-        <v>45773.54166666666</v>
+        <v>45798.77083333334</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>US Catanzaro 1929</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>Spezia</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>(0a7b3b129a758de5a07b8bb3a734143b,2024-12-21T16:15:00Z)</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ea580d732237a7eeaeed18161b4a5971</t>
+          <t>c997d7ac213331536d69d6c70151c3d7</t>
         </is>
       </c>
       <c r="B161" s="2" t="n">
-        <v>45773.63541666666</v>
+        <v>45798.77083333334</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>US Catanzaro 1929</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Palermo</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr"/>
+          <t>Cremonese</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>(0b7f6a1e8c5f2f6c0677a306bb4605cc,2024-10-20T13:00:00Z)</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>3d61cdda97e58eee8fb2f52c363e8a74</t>
+          <t>1f128259b8beccd1058058ef07df226d</t>
         </is>
       </c>
       <c r="B162" s="2" t="n">
-        <v>45773.66666666666</v>
+        <v>45830.77083333334</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>1d11ec7d023cb74d7c9db7be2d2bdf4c</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="n">
-        <v>45773.78125</v>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>13e6d3c39741630996872d9edf36392a</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="n">
-        <v>45792.70833333334</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>CA Osasuna</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Atlético Madrid</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>9ad64f2ea5f9848306b5e2e22a903597</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="n">
-        <v>45795.54166666666</v>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Atalanta BC</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>0ff442300bab3d44bf09d1e6855a2cae</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="n">
-        <v>45798.77083333334</v>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>US Catanzaro 1929</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>Spezia</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>(0a7b3b129a758de5a07b8bb3a734143b,2024-12-21T16:15:00Z)</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>c997d7ac213331536d69d6c70151c3d7</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="n">
-        <v>45798.77083333334</v>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Juve Stabia</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Cremonese</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>(0b7f6a1e8c5f2f6c0677a306bb4605cc,2024-10-20T13:00:00Z)</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>1f128259b8beccd1058058ef07df226d</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="n">
-        <v>45830.77083333334</v>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Salernitana</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Sampdoria</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/service_ia/dataset/analyze_none_id.xlsx
+++ b/service_ia/dataset/analyze_none_id.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,11 @@
           <t>id_fixture_from_stat</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>original_index</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -485,6 +490,9 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>1900</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -507,6 +515,9 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>1897</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -529,6 +540,9 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>1896</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -551,6 +565,9 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>1899</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -573,6 +590,9 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>1903</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -595,6 +615,9 @@
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>1902</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -617,6 +640,9 @@
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>1905</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -639,6 +665,9 @@
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>1904</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -661,6 +690,9 @@
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>6602</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -683,6 +715,9 @@
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>6611</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -705,6 +740,9 @@
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>6609</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -727,6 +765,9 @@
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
+      <c r="G13" t="n">
+        <v>6625</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -749,6 +790,9 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>6627</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -771,6 +815,9 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
+      <c r="G15" t="n">
+        <v>6621</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -793,6 +840,9 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>6620</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -815,6 +865,9 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
+      <c r="G17" t="n">
+        <v>3255</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -837,6 +890,9 @@
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
+      <c r="G18" t="n">
+        <v>3256</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -859,6 +915,9 @@
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>8481</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -881,6 +940,9 @@
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>1988</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -903,6 +965,9 @@
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>1995</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -925,6 +990,9 @@
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
+        <v>2008</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -947,6 +1015,9 @@
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>3359</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -969,6 +1040,9 @@
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
+        <v>3373</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -991,6 +1065,9 @@
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>8585</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1013,6 +1090,9 @@
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
+        <v>266</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1035,6 +1115,9 @@
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
+        <v>8680</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1061,6 +1144,9 @@
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>8685</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1083,6 +1169,9 @@
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>2130</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1105,6 +1194,9 @@
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
+        <v>3522</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1131,6 +1223,9 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
+        <v>8783</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1153,6 +1248,9 @@
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>579</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1175,6 +1273,9 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
+        <v>573</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1197,6 +1298,9 @@
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
+        <v>583</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1219,6 +1323,9 @@
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
+        <v>2255</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1245,6 +1352,9 @@
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>2254</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1271,6 +1381,9 @@
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
+        <v>2253</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1297,6 +1410,9 @@
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
+        <v>2262</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1319,6 +1435,9 @@
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>730</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1341,6 +1460,9 @@
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
+        <v>727</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1363,6 +1485,9 @@
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>728</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1385,6 +1510,9 @@
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>729</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1407,6 +1535,9 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
+      <c r="G43" t="n">
+        <v>7308</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1429,6 +1560,9 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>3982</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1451,6 +1585,9 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
+      <c r="G45" t="n">
+        <v>1066</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1473,6 +1610,9 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
+      <c r="G46" t="n">
+        <v>1114</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1495,6 +1635,9 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
+      <c r="G47" t="n">
+        <v>1115</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1517,6 +1660,9 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
+      <c r="G48" t="n">
+        <v>7850</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1539,6 +1685,9 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>7904</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1561,6 +1710,9 @@
       </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
+      <c r="G50" t="n">
+        <v>7912</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1583,6 +1735,9 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
+      <c r="G51" t="n">
+        <v>1450</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1605,6 +1760,9 @@
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>1468</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1627,6 +1785,9 @@
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
+      <c r="G53" t="n">
+        <v>1467</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1649,6 +1810,9 @@
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>1471</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1671,6 +1835,9 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
+      <c r="G55" t="n">
+        <v>1466</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1693,6 +1860,9 @@
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
+      <c r="G56" t="n">
+        <v>1465</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1715,6 +1885,9 @@
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
+      <c r="G57" t="n">
+        <v>1495</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1737,6 +1910,9 @@
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
+      <c r="G58" t="n">
+        <v>1498</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1759,6 +1935,9 @@
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>1501</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1781,6 +1960,9 @@
       </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
+      <c r="G60" t="n">
+        <v>1500</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1803,6 +1985,9 @@
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
+      <c r="G61" t="n">
+        <v>1499</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1825,6 +2010,9 @@
       </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>1497</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1851,6 +2039,9 @@
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>1564</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1873,6 +2064,9 @@
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>1641</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1895,6 +2089,9 @@
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>8187</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1917,6 +2114,9 @@
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>8188</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1939,6 +2139,9 @@
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
+      <c r="G67" t="n">
+        <v>8241</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1961,6 +2164,9 @@
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
+      <c r="G68" t="n">
+        <v>8243</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1983,6 +2189,9 @@
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
+      <c r="G69" t="n">
+        <v>1738</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2005,6 +2214,9 @@
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
+      <c r="G70" t="n">
+        <v>8302</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2027,6 +2239,9 @@
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
+      <c r="G71" t="n">
+        <v>1769</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2049,6 +2264,9 @@
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>8305</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2071,6 +2289,9 @@
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>3100</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2093,6 +2314,9 @@
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
+      <c r="G74" t="n">
+        <v>1831</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2115,6 +2339,9 @@
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
+      <c r="G75" t="n">
+        <v>1832</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2137,6 +2364,9 @@
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
+      <c r="G76" t="n">
+        <v>1833</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2159,6 +2389,9 @@
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
+      <c r="G77" t="n">
+        <v>1834</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2181,6 +2414,9 @@
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>1835</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2203,6 +2439,9 @@
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
+      <c r="G79" t="n">
+        <v>3143</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2225,6 +2464,9 @@
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
+      <c r="G80" t="n">
+        <v>1836</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2247,6 +2489,9 @@
       </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
+      <c r="G81" t="n">
+        <v>3144</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2269,6 +2514,9 @@
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>1837</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2291,6 +2539,9 @@
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
+      <c r="G83" t="n">
+        <v>1838</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2313,6 +2564,9 @@
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>1866</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2335,6 +2589,9 @@
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
+      <c r="G85" t="n">
+        <v>3169</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
